--- a/Testing_Data/2022_02_Festo/Results_table_10mm_pinned_LoadCell.xlsx
+++ b/Testing_Data/2022_02_Festo/Results_table_10mm_pinned_LoadCell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2022_02_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97047E0-B82B-4F65-A0C1-C460909C2F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2334CD85-7457-4F7C-9FFE-4CDF509178B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -19,9 +19,10 @@
     <sheet name="ExtTest10mm_4" sheetId="12" r:id="rId4"/>
     <sheet name="ExtTest10mm_5" sheetId="13" r:id="rId5"/>
     <sheet name="ExtTest10mm_6" sheetId="14" r:id="rId6"/>
-    <sheet name="FlxTest10mm_1" sheetId="7" r:id="rId7"/>
-    <sheet name="FlxTest10mm_2" sheetId="8" r:id="rId8"/>
-    <sheet name="FlxTest10mm_3" sheetId="15" r:id="rId9"/>
+    <sheet name="ExtTest10mm_7" sheetId="16" r:id="rId7"/>
+    <sheet name="FlxTest10mm_1" sheetId="7" r:id="rId8"/>
+    <sheet name="FlxTest10mm_2" sheetId="8" r:id="rId9"/>
+    <sheet name="FlxTest10mm_3" sheetId="15" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="47">
   <si>
     <t>Test #</t>
   </si>
@@ -182,6 +183,9 @@
   </si>
   <si>
     <t>original</t>
+  </si>
+  <si>
+    <t>^Collected by Ben and Moe</t>
   </si>
 </sst>
 </file>
@@ -991,6 +995,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -998,7 +1003,454 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.35160629921259845"/>
+                  <c:y val="-0.12492964421114028"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.13252318460192475"/>
+                  <c:y val="1.6458880139982501E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_3!$C$7:$L$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>-41</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-45</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-57</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-63</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-77</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-75</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-80</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-90</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-95</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-105</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_3!$C$15:$L$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>-17.623982271657447</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-14.312588392743191</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-10.544115710489031</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-7.714703040370237</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-5.2633492521046072</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-5.0482353303594207</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-2.8329795466253955</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1.807118322254111</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1.0285393197546095</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.56161756164602195</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1E1B-4C83-AE53-4FC10967BF8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="497510136"/>
+        <c:axId val="497510792"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="497510136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="497510792"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="497510792"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="497510136"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1662,6 +2114,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1669,7 +2122,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2142,6 +2594,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2149,7 +2602,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2739,6 +3191,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2746,7 +3199,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3211,6 +3663,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3218,7 +3671,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3687,6 +4139,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3694,7 +4147,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3730,6 +4182,413 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.30954483814523187"/>
+                  <c:y val="-2.5762248468941384E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>ExtTest10mm_7!$C$7:$AE$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>1.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>ExtTest10mm_7!$C$15:$AE$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>0.55424608033235112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6160-49D9-AAA9-100CB6C445C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="495425744"/>
+        <c:axId val="495426728"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="495425744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="495426728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="495426728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="495425744"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4340,6 +5199,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4347,7 +5207,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4382,7 +5241,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4969,6 +5828,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4976,455 +5836,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.35160629921259845"/>
-                  <c:y val="-0.12492964421114028"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="3"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.13252318460192475"/>
-                  <c:y val="1.6458880139982501E-3"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>FlxTest10mm_3!$C$7:$L$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>-41</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-45</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-57</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-63</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-77</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-75</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-80</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-90</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-95</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-105</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>FlxTest10mm_3!$C$15:$L$15</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>-17.623982271657447</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-14.312588392743191</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-10.544115710489031</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-7.714703040370237</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-5.2633492521046072</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-5.0482353303594207</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-2.8329795466253955</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-1.807118322254111</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-1.0285393197546095</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-0.56161756164602195</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1E1B-4C83-AE53-4FC10967BF8E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="497510136"/>
-        <c:axId val="497510792"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="497510136"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="497510792"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="497510792"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="497510136"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5460,6 +5871,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -6335,6 +6786,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -10490,6 +11457,47 @@
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>500062</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>528637</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87F016FD-8475-49B9-BE00-EEAE24A59AD9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -10721,6 +11729,49 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>338137</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>80962</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04282C09-B451-4213-BA14-32757C772568}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>740833</xdr:colOff>
       <xdr:row>20</xdr:row>
@@ -10760,7 +11811,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -10787,47 +11838,6 @@
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>500062</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>528637</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87F016FD-8475-49B9-BE00-EEAE24A59AD9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -12093,6 +13103,680 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB28D160-17A5-469E-8CF6-067E3CB95279}">
+  <dimension ref="A1:AJ29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>457</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <f>C2-C2*0.17</f>
+        <v>379.31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <f>P5+1</f>
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <f>Q5+1</f>
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <f t="shared" ref="S5:AI5" si="0">R5+1</f>
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="AG5" s="10">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="AH5" s="10">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="AI5" s="10">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>67.698999999999998</v>
+      </c>
+      <c r="D6">
+        <v>53.807000000000002</v>
+      </c>
+      <c r="E6">
+        <v>40.158999999999999</v>
+      </c>
+      <c r="F6">
+        <v>29.155000000000001</v>
+      </c>
+      <c r="G6">
+        <v>19.347000000000001</v>
+      </c>
+      <c r="H6">
+        <v>18.911000000000001</v>
+      </c>
+      <c r="I6">
+        <v>10.577</v>
+      </c>
+      <c r="J6">
+        <v>6.6810999999999998</v>
+      </c>
+      <c r="K6">
+        <v>3.8237000000000001</v>
+      </c>
+      <c r="L6">
+        <v>2.0994000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>-41</v>
+      </c>
+      <c r="D7">
+        <v>-45</v>
+      </c>
+      <c r="E7">
+        <v>-57</v>
+      </c>
+      <c r="F7">
+        <v>-63</v>
+      </c>
+      <c r="G7">
+        <v>-77</v>
+      </c>
+      <c r="H7">
+        <v>-75</v>
+      </c>
+      <c r="I7">
+        <v>-80</v>
+      </c>
+      <c r="J7">
+        <v>-90</v>
+      </c>
+      <c r="K7">
+        <v>-95</v>
+      </c>
+      <c r="L7">
+        <v>-105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
+        <v>71.2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>75.3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>72.7</v>
+      </c>
+      <c r="F8" s="1">
+        <v>74.2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="H8" s="1">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="I8" s="1">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="J8" s="1">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="K8" s="1">
+        <v>78</v>
+      </c>
+      <c r="L8" s="1">
+        <v>76.599999999999994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A9" s="12"/>
+      <c r="B9" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>428</v>
+      </c>
+      <c r="D10">
+        <v>418</v>
+      </c>
+      <c r="E10">
+        <v>409.5</v>
+      </c>
+      <c r="F10">
+        <v>405.5</v>
+      </c>
+      <c r="G10">
+        <v>395</v>
+      </c>
+      <c r="H10">
+        <v>396</v>
+      </c>
+      <c r="I10">
+        <v>390</v>
+      </c>
+      <c r="J10">
+        <v>384</v>
+      </c>
+      <c r="K10">
+        <v>381</v>
+      </c>
+      <c r="L10">
+        <v>376</v>
+      </c>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="2"/>
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="2"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="2"/>
+      <c r="AI10" s="2"/>
+      <c r="AJ10" s="2"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>275</v>
+      </c>
+      <c r="D12">
+        <v>275</v>
+      </c>
+      <c r="E12">
+        <v>275</v>
+      </c>
+      <c r="F12">
+        <v>275</v>
+      </c>
+      <c r="G12">
+        <v>275</v>
+      </c>
+      <c r="H12">
+        <v>275</v>
+      </c>
+      <c r="I12">
+        <v>275</v>
+      </c>
+      <c r="J12">
+        <v>275</v>
+      </c>
+      <c r="K12">
+        <v>275</v>
+      </c>
+      <c r="L12">
+        <v>275</v>
+      </c>
+      <c r="M12">
+        <v>275</v>
+      </c>
+      <c r="N12">
+        <v>275</v>
+      </c>
+      <c r="O12">
+        <v>275</v>
+      </c>
+      <c r="P12">
+        <v>275</v>
+      </c>
+      <c r="Q12">
+        <v>275</v>
+      </c>
+      <c r="R12">
+        <v>275</v>
+      </c>
+      <c r="S12">
+        <v>275</v>
+      </c>
+      <c r="T12">
+        <v>275</v>
+      </c>
+      <c r="U12">
+        <v>275</v>
+      </c>
+      <c r="V12">
+        <v>275</v>
+      </c>
+      <c r="W12">
+        <v>275</v>
+      </c>
+      <c r="X12">
+        <v>275</v>
+      </c>
+      <c r="Y12">
+        <v>275</v>
+      </c>
+      <c r="Z12">
+        <v>275</v>
+      </c>
+      <c r="AA12">
+        <v>275</v>
+      </c>
+      <c r="AB12">
+        <v>275</v>
+      </c>
+      <c r="AC12">
+        <v>275</v>
+      </c>
+      <c r="AD12">
+        <v>275</v>
+      </c>
+      <c r="AE12">
+        <v>275</v>
+      </c>
+      <c r="AF12">
+        <v>275</v>
+      </c>
+      <c r="AG12">
+        <v>275</v>
+      </c>
+      <c r="AH12">
+        <v>275</v>
+      </c>
+      <c r="AI12">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>80</v>
+      </c>
+      <c r="D13">
+        <v>81</v>
+      </c>
+      <c r="E13">
+        <v>78</v>
+      </c>
+      <c r="F13">
+        <v>76</v>
+      </c>
+      <c r="G13">
+        <v>62</v>
+      </c>
+      <c r="H13">
+        <v>62.5</v>
+      </c>
+      <c r="I13">
+        <v>60</v>
+      </c>
+      <c r="J13">
+        <v>48</v>
+      </c>
+      <c r="K13">
+        <v>34</v>
+      </c>
+      <c r="L13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13"/>
+      <c r="B14" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="B15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <f>C6*-SIN(RADIANS(C8))*C12/1000</f>
+        <v>-17.623982271657447</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ref="D15:AI15" si="1">D6*-SIN(RADIANS(D8))*D12/1000</f>
+        <v>-14.312588392743191</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>-10.544115710489031</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>-7.714703040370237</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>-5.2633492521046072</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>-5.0482353303594207</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="1"/>
+        <v>-2.8329795466253955</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>-1.807118322254111</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>-1.0285393197546095</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>-0.56161756164602195</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="10:18" x14ac:dyDescent="0.3">
+      <c r="J18">
+        <f>1-348/457</f>
+        <v>0.23851203501094087</v>
+      </c>
+    </row>
+    <row r="29" spans="10:18" x14ac:dyDescent="0.3">
+      <c r="R29">
+        <f>485*1.03</f>
+        <v>499.55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D1208C-7CDD-421F-9FF0-096EE144B4F3}">
   <dimension ref="A1:AJ15"/>
@@ -15716,6 +17400,382 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07511B1B-CFA9-4E3E-A27D-F86FFAE12463}">
+  <dimension ref="A1:AE15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="3"/>
+    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>403</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>2.2372000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1">
+        <v>82.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A9" s="12"/>
+      <c r="B9" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A11" s="12"/>
+      <c r="B11" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>249.71</v>
+      </c>
+      <c r="D12">
+        <v>249.71</v>
+      </c>
+      <c r="E12">
+        <v>249.71</v>
+      </c>
+      <c r="F12">
+        <v>249.71</v>
+      </c>
+      <c r="G12">
+        <v>249.71</v>
+      </c>
+      <c r="H12">
+        <v>249.71</v>
+      </c>
+      <c r="I12">
+        <v>249.71</v>
+      </c>
+      <c r="J12">
+        <v>249.71</v>
+      </c>
+      <c r="K12">
+        <v>249.71</v>
+      </c>
+      <c r="L12">
+        <v>249.71</v>
+      </c>
+      <c r="M12">
+        <v>249.71</v>
+      </c>
+      <c r="N12">
+        <v>249.71</v>
+      </c>
+      <c r="O12">
+        <v>249.71</v>
+      </c>
+      <c r="P12">
+        <v>249.71</v>
+      </c>
+      <c r="Q12">
+        <v>249.71</v>
+      </c>
+      <c r="R12">
+        <v>249.71</v>
+      </c>
+      <c r="S12">
+        <v>249.71</v>
+      </c>
+      <c r="AA12">
+        <v>249.71</v>
+      </c>
+      <c r="AB12">
+        <v>249.71</v>
+      </c>
+      <c r="AC12">
+        <v>249.71</v>
+      </c>
+      <c r="AD12">
+        <v>249.71</v>
+      </c>
+      <c r="AE12">
+        <v>249.71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13"/>
+      <c r="B14" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <f>C6*SIN(RADIANS(C8))*C12/1000</f>
+        <v>0.55424608033235112</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ref="D15:S15" si="0">D6*SIN(RADIANS(D8))*D12/1000</f>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" ref="D15:AE15" si="1">AA6*SIN(RADIANS(AA8))*AA12/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E5B9E9-F1B4-4DAB-B7CA-9BCB2303132C}">
   <dimension ref="A1:AJ15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -16614,7 +18674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245A1644-2BFB-4EA7-BEAA-4598893697AD}">
   <dimension ref="A1:AJ29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -17431,678 +19491,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB28D160-17A5-469E-8CF6-067E3CB95279}">
-  <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>457</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3">
-        <f>C2-C2*0.17</f>
-        <v>379.31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1</v>
-      </c>
-      <c r="D5" s="10">
-        <v>2</v>
-      </c>
-      <c r="E5" s="10">
-        <v>3</v>
-      </c>
-      <c r="F5" s="10">
-        <v>4</v>
-      </c>
-      <c r="G5" s="10">
-        <v>5</v>
-      </c>
-      <c r="H5" s="10">
-        <v>6</v>
-      </c>
-      <c r="I5" s="10">
-        <v>7</v>
-      </c>
-      <c r="J5" s="10">
-        <v>8</v>
-      </c>
-      <c r="K5" s="10">
-        <v>9</v>
-      </c>
-      <c r="L5" s="10">
-        <v>10</v>
-      </c>
-      <c r="M5" s="10">
-        <v>11</v>
-      </c>
-      <c r="N5" s="10">
-        <v>12</v>
-      </c>
-      <c r="O5" s="10">
-        <v>13</v>
-      </c>
-      <c r="P5" s="10">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="10">
-        <f>P5+1</f>
-        <v>15</v>
-      </c>
-      <c r="R5" s="10">
-        <f>Q5+1</f>
-        <v>16</v>
-      </c>
-      <c r="S5" s="10">
-        <f t="shared" ref="S5:AI5" si="0">R5+1</f>
-        <v>17</v>
-      </c>
-      <c r="T5" s="10">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="U5" s="10">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="V5" s="10">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="W5" s="10">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="X5" s="10">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Y5" s="10">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="Z5" s="10">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AA5" s="10">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AB5" s="10">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AC5" s="10">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="AD5" s="10">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="AE5" s="10">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="AF5" s="10">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="AG5" s="10">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="AH5" s="10">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="AI5" s="10">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="B6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>67.698999999999998</v>
-      </c>
-      <c r="D6">
-        <v>53.807000000000002</v>
-      </c>
-      <c r="E6">
-        <v>40.158999999999999</v>
-      </c>
-      <c r="F6">
-        <v>29.155000000000001</v>
-      </c>
-      <c r="G6">
-        <v>19.347000000000001</v>
-      </c>
-      <c r="H6">
-        <v>18.911000000000001</v>
-      </c>
-      <c r="I6">
-        <v>10.577</v>
-      </c>
-      <c r="J6">
-        <v>6.6810999999999998</v>
-      </c>
-      <c r="K6">
-        <v>3.8237000000000001</v>
-      </c>
-      <c r="L6">
-        <v>2.0994000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>-41</v>
-      </c>
-      <c r="D7">
-        <v>-45</v>
-      </c>
-      <c r="E7">
-        <v>-57</v>
-      </c>
-      <c r="F7">
-        <v>-63</v>
-      </c>
-      <c r="G7">
-        <v>-77</v>
-      </c>
-      <c r="H7">
-        <v>-75</v>
-      </c>
-      <c r="I7">
-        <v>-80</v>
-      </c>
-      <c r="J7">
-        <v>-90</v>
-      </c>
-      <c r="K7">
-        <v>-95</v>
-      </c>
-      <c r="L7">
-        <v>-105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1">
-        <v>71.2</v>
-      </c>
-      <c r="D8" s="1">
-        <v>75.3</v>
-      </c>
-      <c r="E8" s="1">
-        <v>72.7</v>
-      </c>
-      <c r="F8" s="1">
-        <v>74.2</v>
-      </c>
-      <c r="G8" s="1">
-        <v>81.599999999999994</v>
-      </c>
-      <c r="H8" s="1">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="I8" s="1">
-        <v>76.900000000000006</v>
-      </c>
-      <c r="J8" s="1">
-        <v>79.599999999999994</v>
-      </c>
-      <c r="K8" s="1">
-        <v>78</v>
-      </c>
-      <c r="L8" s="1">
-        <v>76.599999999999994</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>428</v>
-      </c>
-      <c r="D10">
-        <v>418</v>
-      </c>
-      <c r="E10">
-        <v>409.5</v>
-      </c>
-      <c r="F10">
-        <v>405.5</v>
-      </c>
-      <c r="G10">
-        <v>395</v>
-      </c>
-      <c r="H10">
-        <v>396</v>
-      </c>
-      <c r="I10">
-        <v>390</v>
-      </c>
-      <c r="J10">
-        <v>384</v>
-      </c>
-      <c r="K10">
-        <v>381</v>
-      </c>
-      <c r="L10">
-        <v>376</v>
-      </c>
-      <c r="M10"/>
-      <c r="N10"/>
-      <c r="O10"/>
-      <c r="P10"/>
-      <c r="Q10"/>
-      <c r="R10"/>
-      <c r="S10"/>
-      <c r="T10"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
-      <c r="AB10" s="2"/>
-      <c r="AC10" s="2"/>
-      <c r="AD10" s="2"/>
-      <c r="AE10" s="2"/>
-      <c r="AF10" s="2"/>
-      <c r="AG10" s="2"/>
-      <c r="AH10" s="2"/>
-      <c r="AI10" s="2"/>
-      <c r="AJ10" s="2"/>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>275</v>
-      </c>
-      <c r="D12">
-        <v>275</v>
-      </c>
-      <c r="E12">
-        <v>275</v>
-      </c>
-      <c r="F12">
-        <v>275</v>
-      </c>
-      <c r="G12">
-        <v>275</v>
-      </c>
-      <c r="H12">
-        <v>275</v>
-      </c>
-      <c r="I12">
-        <v>275</v>
-      </c>
-      <c r="J12">
-        <v>275</v>
-      </c>
-      <c r="K12">
-        <v>275</v>
-      </c>
-      <c r="L12">
-        <v>275</v>
-      </c>
-      <c r="M12">
-        <v>275</v>
-      </c>
-      <c r="N12">
-        <v>275</v>
-      </c>
-      <c r="O12">
-        <v>275</v>
-      </c>
-      <c r="P12">
-        <v>275</v>
-      </c>
-      <c r="Q12">
-        <v>275</v>
-      </c>
-      <c r="R12">
-        <v>275</v>
-      </c>
-      <c r="S12">
-        <v>275</v>
-      </c>
-      <c r="T12">
-        <v>275</v>
-      </c>
-      <c r="U12">
-        <v>275</v>
-      </c>
-      <c r="V12">
-        <v>275</v>
-      </c>
-      <c r="W12">
-        <v>275</v>
-      </c>
-      <c r="X12">
-        <v>275</v>
-      </c>
-      <c r="Y12">
-        <v>275</v>
-      </c>
-      <c r="Z12">
-        <v>275</v>
-      </c>
-      <c r="AA12">
-        <v>275</v>
-      </c>
-      <c r="AB12">
-        <v>275</v>
-      </c>
-      <c r="AC12">
-        <v>275</v>
-      </c>
-      <c r="AD12">
-        <v>275</v>
-      </c>
-      <c r="AE12">
-        <v>275</v>
-      </c>
-      <c r="AF12">
-        <v>275</v>
-      </c>
-      <c r="AG12">
-        <v>275</v>
-      </c>
-      <c r="AH12">
-        <v>275</v>
-      </c>
-      <c r="AI12">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
-      <c r="B13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13">
-        <v>80</v>
-      </c>
-      <c r="D13">
-        <v>81</v>
-      </c>
-      <c r="E13">
-        <v>78</v>
-      </c>
-      <c r="F13">
-        <v>76</v>
-      </c>
-      <c r="G13">
-        <v>62</v>
-      </c>
-      <c r="H13">
-        <v>62.5</v>
-      </c>
-      <c r="I13">
-        <v>60</v>
-      </c>
-      <c r="J13">
-        <v>48</v>
-      </c>
-      <c r="K13">
-        <v>34</v>
-      </c>
-      <c r="L13">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="B15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <f>C6*-SIN(RADIANS(C8))*C12/1000</f>
-        <v>-17.623982271657447</v>
-      </c>
-      <c r="D15">
-        <f t="shared" ref="D15:AI15" si="1">D6*-SIN(RADIANS(D8))*D12/1000</f>
-        <v>-14.312588392743191</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="1"/>
-        <v>-10.544115710489031</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>-7.714703040370237</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>-5.2633492521046072</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>-5.0482353303594207</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>-2.8329795466253955</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>-1.807118322254111</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>-1.0285393197546095</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="1"/>
-        <v>-0.56161756164602195</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="10:18" x14ac:dyDescent="0.3">
-      <c r="J18">
-        <f>1-348/457</f>
-        <v>0.23851203501094087</v>
-      </c>
-    </row>
-    <row r="29" spans="10:18" x14ac:dyDescent="0.3">
-      <c r="R29">
-        <f>485*1.03</f>
-        <v>499.55</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/Testing_Data/2022_02_Festo/Results_table_10mm_pinned_LoadCell.xlsx
+++ b/Testing_Data/2022_02_Festo/Results_table_10mm_pinned_LoadCell.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2022_02_Festo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melze\Documents\GitHub\Bipedal_Robot\Testing_Data\2022_02_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2334CD85-7457-4F7C-9FFE-4CDF509178B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E2FFD0-D404-48A4-A8F9-EE1C8493D8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="4515" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="50">
   <si>
     <t>Test #</t>
   </si>
@@ -187,12 +187,21 @@
   <si>
     <t>^Collected by Ben and Moe</t>
   </si>
+  <si>
+    <t>Pressure (kPa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">* pretensioned to 6 N </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,13 +217,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="13">
@@ -358,10 +379,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -376,12 +398,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{80FC17CE-DAEF-4944-81FC-831B986AF167}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -4316,12 +4346,24 @@
                 <c:pt idx="0">
                   <c:v>1.5</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-32</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ExtTest10mm_7!$C$15:$AE$15</c:f>
+              <c:f>ExtTest10mm_7!$C$16:$AE$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
@@ -4329,16 +4371,16 @@
                   <c:v>0.55424608033235112</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.3956477431127321</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>6.4896197758391105</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>6.6935893235908681</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>5.3064294378181511</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -11731,13 +11773,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>338137</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>80962</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -12152,24 +12194,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C83896A-0586-4C90-B5FD-474633C66A37}">
   <dimension ref="A1:AJ27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -12180,7 +12222,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -12189,7 +12231,7 @@
         <v>403.38</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -12197,7 +12239,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -12320,7 +12362,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -12385,7 +12427,7 @@
         <v>23.167999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -12450,7 +12492,7 @@
         <v>-123</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -12518,13 +12560,13 @@
         <v>84.4</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -12604,7 +12646,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -12630,7 +12672,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -12705,7 +12747,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -12771,13 +12813,13 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -12914,12 +12956,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C18">
         <f>C6+4.6262</f>
         <v>22.176200000000001</v>
@@ -12957,7 +12999,7 @@
         <v>6.3061999999999996</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C19">
         <v>22.176200000000001</v>
       </c>
@@ -12986,12 +13028,12 @@
         <v>6.3061999999999996</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C20" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C21">
         <v>17.55</v>
       </c>
@@ -13020,7 +13062,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.35">
       <c r="T22">
         <v>480</v>
       </c>
@@ -13037,7 +13079,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.35">
       <c r="S23" t="s">
         <v>30</v>
       </c>
@@ -13062,7 +13104,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.35">
       <c r="S24" t="s">
         <v>31</v>
       </c>
@@ -13087,7 +13129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.35">
       <c r="S27" t="s">
         <v>32</v>
       </c>
@@ -13106,24 +13148,24 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB28D160-17A5-469E-8CF6-067E3CB95279}">
   <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -13134,7 +13176,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -13143,7 +13185,7 @@
         <v>379.31</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -13151,7 +13193,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -13274,7 +13316,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -13309,7 +13351,7 @@
         <v>2.0994000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -13344,7 +13386,7 @@
         <v>-105</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -13382,13 +13424,13 @@
         <v>76.599999999999994</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -13448,7 +13490,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -13474,7 +13516,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -13579,7 +13621,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -13615,13 +13657,13 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -13758,13 +13800,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="10:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="10:18" x14ac:dyDescent="0.35">
       <c r="J18">
         <f>1-348/457</f>
         <v>0.23851203501094087</v>
       </c>
     </row>
-    <row r="29" spans="10:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="10:18" x14ac:dyDescent="0.35">
       <c r="R29">
         <f>485*1.03</f>
         <v>499.55</v>
@@ -13780,24 +13822,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D1208C-7CDD-421F-9FF0-096EE144B4F3}">
   <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -13808,7 +13850,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -13817,7 +13859,7 @@
         <v>379.31</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -13829,7 +13871,7 @@
         <v>0.16849015317286653</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -13952,7 +13994,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -14044,7 +14086,7 @@
         <v>24.667000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -14136,7 +14178,7 @@
         <v>-123</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -14231,13 +14273,13 @@
         <v>81.400000000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -14335,7 +14377,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -14361,7 +14403,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -14466,7 +14508,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -14559,13 +14601,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -14712,24 +14754,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23CB8201-A5D3-4826-B613-98BAA3DB341B}">
   <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -14740,7 +14782,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -14749,7 +14791,7 @@
         <v>403.38</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -14761,7 +14803,7 @@
         <v>0.18106995884773658</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -14884,7 +14926,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -14901,7 +14943,7 @@
         <v>13.111000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -14918,7 +14960,7 @@
         <v>-92</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -14938,13 +14980,13 @@
         <v>80.7</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -14992,7 +15034,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -15018,7 +15060,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -15123,7 +15165,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -15141,13 +15183,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -15294,24 +15336,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D539E524-5F19-4B4B-B21A-C95F2596B6A0}">
   <dimension ref="A1:AJ27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -15322,7 +15364,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -15334,7 +15376,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -15355,7 +15397,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -15478,7 +15520,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -15564,7 +15606,7 @@
         <v>33.061999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -15647,7 +15689,7 @@
         <v>-66</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -15733,13 +15775,13 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -15831,7 +15873,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -15857,7 +15899,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -15962,7 +16004,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -16046,13 +16088,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -16189,7 +16231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="U16" t="s">
         <v>23</v>
       </c>
@@ -16197,22 +16239,22 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="17:29" x14ac:dyDescent="0.3">
+    <row r="17" spans="17:29" x14ac:dyDescent="0.35">
       <c r="AB17">
         <v>2.2241</v>
       </c>
     </row>
-    <row r="18" spans="17:29" x14ac:dyDescent="0.3">
+    <row r="18" spans="17:29" x14ac:dyDescent="0.35">
       <c r="AC18" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="17:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q24" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="17:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q25" t="s">
         <v>42</v>
       </c>
@@ -16223,7 +16265,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="17:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q26" t="s">
         <v>43</v>
       </c>
@@ -16234,7 +16276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="17:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="17:29" x14ac:dyDescent="0.35">
       <c r="R27">
         <v>505</v>
       </c>
@@ -16249,24 +16291,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E6C766-4925-4D35-B304-44784D2D9843}">
   <dimension ref="A1:Q16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -16277,7 +16319,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -16285,7 +16327,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -16296,7 +16338,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -16346,7 +16388,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -16393,7 +16435,7 @@
         <v>6.2092000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -16440,7 +16482,7 @@
         <v>-18.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -16490,7 +16532,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>3</v>
@@ -16538,7 +16580,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>8</v>
       </c>
@@ -16546,13 +16588,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -16603,7 +16645,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -16651,13 +16693,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -16722,7 +16764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="L16" t="s">
         <v>39</v>
       </c>
@@ -16737,24 +16779,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B944D1C8-56B8-47D8-90D4-245D22EBCA01}">
   <dimension ref="A1:AE15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -16765,7 +16807,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -16773,7 +16815,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -16781,7 +16823,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -16873,7 +16915,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -16929,7 +16971,7 @@
         <v>17.72</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -16985,7 +17027,7 @@
         <v>-119.5</v>
       </c>
     </row>
-    <row r="8" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -17044,7 +17086,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>3</v>
@@ -17101,7 +17143,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="10" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>8</v>
       </c>
@@ -17109,13 +17151,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -17208,7 +17250,7 @@
         <v>249.71</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -17265,13 +17307,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -17401,25 +17443,26 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07511B1B-CFA9-4E3E-A27D-F86FFAE12463}">
-  <dimension ref="A1:AE15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AE16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="8.90625" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="8" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -17430,7 +17473,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -17438,19 +17481,22 @@
         <v>345</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
+      <c r="H4" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="15">
         <v>1</v>
       </c>
       <c r="D5" s="10">
@@ -17538,232 +17584,317 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="16">
         <v>2.2372000000000001</v>
       </c>
+      <c r="D6">
+        <v>1.6</v>
+      </c>
+      <c r="E6">
+        <v>27.57</v>
+      </c>
+      <c r="F6">
+        <v>28.35</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="16">
         <v>1.5</v>
       </c>
+      <c r="D7">
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>-32</v>
+      </c>
+      <c r="F7">
+        <v>-14</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="B8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="16">
+        <v>620</v>
+      </c>
+      <c r="D8">
+        <v>628</v>
+      </c>
+      <c r="E8">
+        <v>628.1</v>
+      </c>
+      <c r="F8">
+        <v>629.70000000000005</v>
+      </c>
+      <c r="G8">
+        <v>628.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C9" s="17">
         <v>82.8</v>
       </c>
+      <c r="D9" s="1">
+        <v>82</v>
+      </c>
+      <c r="E9" s="1">
+        <v>70.5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>71</v>
+      </c>
+      <c r="G9" s="1">
+        <v>75</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="8" t="s">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C9">
+      <c r="C10" s="16">
         <v>340</v>
       </c>
+      <c r="D10" s="14">
+        <v>334</v>
+      </c>
+      <c r="E10" s="14">
+        <f>260+120</f>
+        <v>380</v>
+      </c>
+      <c r="F10" s="14">
+        <v>373</v>
+      </c>
+      <c r="G10" s="14">
+        <v>357</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
+      <c r="C11" s="17"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="B11" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>249.71</v>
-      </c>
-      <c r="D12">
-        <v>249.71</v>
-      </c>
-      <c r="E12">
-        <v>249.71</v>
-      </c>
-      <c r="F12">
-        <v>249.71</v>
-      </c>
-      <c r="G12">
-        <v>249.71</v>
-      </c>
-      <c r="H12">
-        <v>249.71</v>
-      </c>
-      <c r="I12">
-        <v>249.71</v>
-      </c>
-      <c r="J12">
-        <v>249.71</v>
-      </c>
-      <c r="K12">
-        <v>249.71</v>
-      </c>
-      <c r="L12">
-        <v>249.71</v>
-      </c>
-      <c r="M12">
-        <v>249.71</v>
-      </c>
-      <c r="N12">
-        <v>249.71</v>
-      </c>
-      <c r="O12">
-        <v>249.71</v>
-      </c>
-      <c r="P12">
-        <v>249.71</v>
-      </c>
-      <c r="Q12">
-        <v>249.71</v>
-      </c>
-      <c r="R12">
-        <v>249.71</v>
-      </c>
-      <c r="S12">
-        <v>249.71</v>
-      </c>
-      <c r="AA12">
-        <v>249.71</v>
-      </c>
-      <c r="AB12">
-        <v>249.71</v>
-      </c>
-      <c r="AC12">
-        <v>249.71</v>
-      </c>
-      <c r="AD12">
-        <v>249.71</v>
-      </c>
-      <c r="AE12">
-        <v>249.71</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="16">
+        <v>249.71</v>
+      </c>
+      <c r="D13">
+        <v>249.71</v>
+      </c>
+      <c r="E13">
+        <v>249.71</v>
+      </c>
+      <c r="F13">
+        <v>249.71</v>
+      </c>
+      <c r="G13">
+        <v>249.71</v>
+      </c>
+      <c r="H13">
+        <v>249.71</v>
+      </c>
+      <c r="I13">
+        <v>249.71</v>
+      </c>
+      <c r="J13">
+        <v>249.71</v>
+      </c>
+      <c r="K13">
+        <v>249.71</v>
+      </c>
+      <c r="L13">
+        <v>249.71</v>
+      </c>
+      <c r="M13">
+        <v>249.71</v>
+      </c>
+      <c r="N13">
+        <v>249.71</v>
+      </c>
+      <c r="O13">
+        <v>249.71</v>
+      </c>
+      <c r="P13">
+        <v>249.71</v>
+      </c>
+      <c r="Q13">
+        <v>249.71</v>
+      </c>
+      <c r="R13">
+        <v>249.71</v>
+      </c>
+      <c r="S13">
+        <v>249.71</v>
+      </c>
+      <c r="AA13">
+        <v>249.71</v>
+      </c>
+      <c r="AB13">
+        <v>249.71</v>
+      </c>
+      <c r="AC13">
+        <v>249.71</v>
+      </c>
+      <c r="AD13">
+        <v>249.71</v>
+      </c>
+      <c r="AE13">
+        <v>249.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A14" s="12"/>
+      <c r="B14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C13">
-        <v>55</v>
+      <c r="C14" s="16"/>
+      <c r="D14">
+        <v>70</v>
+      </c>
+      <c r="E14">
+        <v>32.5</v>
+      </c>
+      <c r="F14">
+        <v>41</v>
+      </c>
+      <c r="G14">
+        <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="9" t="s">
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="13"/>
+      <c r="B15" s="9" t="s">
         <v>4</v>
       </c>
+      <c r="C15" s="18"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="B15" s="5" t="s">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C15">
-        <f>C6*SIN(RADIANS(C8))*C12/1000</f>
+      <c r="C16" s="16">
+        <f>C6*SIN(RADIANS(C9))*C13/1000</f>
         <v>0.55424608033235112</v>
       </c>
-      <c r="D15">
-        <f t="shared" ref="D15:S15" si="0">D6*SIN(RADIANS(D8))*D12/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E15">
+      <c r="D16">
+        <f t="shared" ref="D16:S16" si="0">D6*SIN(RADIANS(D9))*D13/1000</f>
+        <v>0.3956477431127321</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>6.4896197758391105</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>6.6935893235908681</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>5.3064294378181511</v>
+      </c>
+      <c r="H16" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15">
+      <c r="J16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G15">
+      <c r="K16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15">
+      <c r="L16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15">
+      <c r="M16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15">
+      <c r="N16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K15">
+      <c r="O16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L15">
+      <c r="P16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M15">
+      <c r="Q16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N15">
+      <c r="R16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O15">
+      <c r="S16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P15">
-        <f t="shared" si="0"/>
+      <c r="AA16">
+        <f t="shared" ref="AA16:AE16" si="1">AA6*SIN(RADIANS(AA9))*AA13/1000</f>
         <v>0</v>
       </c>
-      <c r="Q15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <f t="shared" ref="D15:AE15" si="1">AA6*SIN(RADIANS(AA8))*AA12/1000</f>
-        <v>0</v>
-      </c>
-      <c r="AB15">
+      <c r="AB16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -17778,24 +17909,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E5B9E9-F1B4-4DAB-B7CA-9BCB2303132C}">
   <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -17806,7 +17937,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -17815,7 +17946,7 @@
         <v>402.55</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -17823,7 +17954,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -17946,7 +18077,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -18035,7 +18166,7 @@
         <v>30.405999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -18124,7 +18255,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -18216,13 +18347,13 @@
         <v>118.5</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -18318,7 +18449,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -18344,7 +18475,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -18434,7 +18565,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -18524,13 +18655,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -18677,24 +18808,24 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245A1644-2BFB-4EA7-BEAA-4598893697AD}">
   <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="19.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -18705,7 +18836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -18717,7 +18848,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -18728,7 +18859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -18851,7 +18982,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -18916,7 +19047,7 @@
         <v>48.012999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -18981,7 +19112,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -19049,13 +19180,13 @@
         <v>95.1</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -19135,7 +19266,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
@@ -19161,7 +19292,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
@@ -19266,7 +19397,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>11</v>
@@ -19332,13 +19463,13 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
@@ -19475,12 +19606,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="L16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="18:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="18:18" x14ac:dyDescent="0.35">
       <c r="R29">
         <f>485*1.03</f>
         <v>499.55</v>

--- a/Testing_Data/2022_02_Festo/Results_table_10mm_pinned_LoadCell.xlsx
+++ b/Testing_Data/2022_02_Festo/Results_table_10mm_pinned_LoadCell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melze\Documents\GitHub\Bipedal_Robot\Testing_Data\2022_02_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E2FFD0-D404-48A4-A8F9-EE1C8493D8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3C8C45-CA98-4C60-AD32-5E8696B98350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4515" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" firstSheet="6" activeTab="7" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest10mm_1" sheetId="9" r:id="rId1"/>
@@ -20,9 +20,10 @@
     <sheet name="ExtTest10mm_5" sheetId="13" r:id="rId5"/>
     <sheet name="ExtTest10mm_6" sheetId="14" r:id="rId6"/>
     <sheet name="ExtTest10mm_7" sheetId="16" r:id="rId7"/>
-    <sheet name="FlxTest10mm_1" sheetId="7" r:id="rId8"/>
-    <sheet name="FlxTest10mm_2" sheetId="8" r:id="rId9"/>
-    <sheet name="FlxTest10mm_3" sheetId="15" r:id="rId10"/>
+    <sheet name="ExtTest10mm_8" sheetId="18" r:id="rId8"/>
+    <sheet name="FlxTest10mm_1" sheetId="7" r:id="rId9"/>
+    <sheet name="FlxTest10mm_2" sheetId="8" r:id="rId10"/>
+    <sheet name="FlxTest10mm_3" sheetId="15" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="52">
   <si>
     <t>Test #</t>
   </si>
@@ -196,12 +197,18 @@
   <si>
     <t xml:space="preserve">* pretensioned to 6 N </t>
   </si>
+  <si>
+    <t>10 N pre tension</t>
+  </si>
+  <si>
+    <t>7n pre T</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,8 +231,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -235,6 +249,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -383,7 +403,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -403,6 +423,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -772,7 +799,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>4.6268503604248918</c:v>
+                  <c:v>0.26363819717520748</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>4.503204045949718</c:v>
@@ -1068,6 +1095,635 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Flexor 10mm</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Knee Torque</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.4158344861650378E-2"/>
+          <c:y val="0.17072497123130037"/>
+          <c:w val="0.91627572927286405"/>
+          <c:h val="0.77864211737629463"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="power"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.60346456692913386"/>
+                  <c:y val="-0.28313193524076818"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.40762374401637524"/>
+                  <c:y val="4.5584595515824444E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_2!$C$7:$AI$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-26.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-42.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-56</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-56</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-63</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-64</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-55</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-48</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-42</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-35</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-26</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-19</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-11</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>11.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>FlxTest10mm_2!$C$15:$AI$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>-12.024486481310953</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-12.010720430450908</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-12.467074331666348</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-11.429265093789359</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-9.361208446969103</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-7.6761795853386783</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.9579976724776733</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1.6722536503811283</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.80746439223476663</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-3.5743411708348779E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-2.0198749999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-4.1705971185958441</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-6.4666790193515293</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-8.1665094852463582</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-10.603302506170124</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-12.640024275140153</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-13.930450567806828</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-14.689482923460329</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-14.674822536018389</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-13.151302910231001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-9D05-4463-B8B4-EFE1AE46B75E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1394438799"/>
+        <c:axId val="1190584639"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1394438799"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1190584639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1190584639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1394438799"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4645,36 +5301,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Flexor 10mm</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> Knee Torque</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4706,17 +5332,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.4158344861650378E-2"/>
-          <c:y val="0.17072497123130037"/>
-          <c:w val="0.91627572927286405"/>
-          <c:h val="0.77864211737629463"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -4755,98 +5371,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="power"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="log"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.60346456692913386"/>
-                  <c:y val="-0.28313193524076818"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="log"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:trendlineType val="poly"/>
             <c:order val="3"/>
             <c:dispRSqr val="1"/>
@@ -4854,8 +5378,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.27899278215223094"/>
-                  <c:y val="0.3201971535736251"/>
+                  <c:x val="-0.30954483814523187"/>
+                  <c:y val="-2.5762248468941384E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -4890,200 +5414,122 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>FlxTest10mm_1!$C$7:$AI$7</c:f>
+              <c:f>ExtTest10mm_8!$C$7:$AE$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>-5.5</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-10.5</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-25.5</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-4.5</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-14.5</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-20</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-33</c:v>
+                  <c:v>-9</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-39.5</c:v>
+                  <c:v>-25</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-43</c:v>
+                  <c:v>-29</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-50</c:v>
+                  <c:v>-30</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-62.5</c:v>
+                  <c:v>-40</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-60</c:v>
+                  <c:v>-69</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-55</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>-53.5</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>-46</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>-40</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>-36.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>-33.5</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>-29.5</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>-24.5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>-17.5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>-14.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>-5.5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>-3</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>-0.5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>3.5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>11.5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>19.5</c:v>
+                  <c:v>-73</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>FlxTest10mm_1!$C$15:$AI$15</c:f>
+              <c:f>ExtTest10mm_8!$C$16:$AE$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>-13.550199438030189</c:v>
+                  <c:v>0.24936778112356464</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12.715746326203965</c:v>
+                  <c:v>1.5180055651816151</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-12.227450296743585</c:v>
+                  <c:v>4.1916022603192538</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-13.574295183417183</c:v>
+                  <c:v>5.7922384740607207</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-12.617833179689791</c:v>
+                  <c:v>7.4880049100902237</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-11.427173303326315</c:v>
+                  <c:v>8.4730476326811974</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-7.8289359826583684</c:v>
+                  <c:v>8.7625994980529605</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-6.4962395866945686</c:v>
+                  <c:v>8.4735529621225449</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-4.9404873370427511</c:v>
+                  <c:v>8.0320045581520194</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-2.8261340010696823</c:v>
+                  <c:v>7.5426084152031541</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1.2108000422274927</c:v>
+                  <c:v>7.7184428186445837</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.11021594724709009</c:v>
+                  <c:v>9.4654641103771695</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1.5137448723481624</c:v>
+                  <c:v>8.9788371589935139</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-3.1927408242720881</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-4.8615958230354943</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-6.8694525901110115</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-8.5997889837959107</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>-10.35823139969961</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>-11.863637901467659</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>-13.477555041999489</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>-13.77813076308844</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>-14.884597105183458</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>-14.534539473342328</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>-14.338144060893327</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-14.021223986689929</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-12.539046654783448</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-11.167854768300959</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-8.2836070695559112</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="32">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5092,7 +5538,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-B771-4C56-A69D-B7F3E808952B}"/>
+              <c16:uniqueId val="{00000001-3FD1-4D6B-B815-E22A8BA0F091}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5104,11 +5550,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1394438799"/>
-        <c:axId val="1190584639"/>
+        <c:axId val="495425744"/>
+        <c:axId val="495426728"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1394438799"/>
+        <c:axId val="495425744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5165,12 +5611,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1190584639"/>
+        <c:crossAx val="495426728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1190584639"/>
+        <c:axId val="495426728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5227,7 +5673,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1394438799"/>
+        <c:crossAx val="495425744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5507,8 +5953,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.40762374401637524"/>
-                  <c:y val="4.5584595515824444E-2"/>
+                  <c:x val="-0.27899278215223094"/>
+                  <c:y val="0.3201971535736251"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -5543,162 +5989,186 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>FlxTest10mm_2!$C$7:$AI$7</c:f>
+              <c:f>FlxTest10mm_1!$C$7:$AI$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>6</c:v>
+                  <c:v>-5.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.5</c:v>
+                  <c:v>-10.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1</c:v>
+                  <c:v>-25.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-15</c:v>
+                  <c:v>-4.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-26.6</c:v>
+                  <c:v>-14.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-35</c:v>
+                  <c:v>-20</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-42.5</c:v>
+                  <c:v>-33</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-56</c:v>
+                  <c:v>-39.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-56</c:v>
+                  <c:v>-43</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-63</c:v>
+                  <c:v>-50</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-64</c:v>
+                  <c:v>-62.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>-60</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>-55</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>-48</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>-42</c:v>
+                  <c:v>-53.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-35</c:v>
+                  <c:v>-46</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-26</c:v>
+                  <c:v>-40</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-19</c:v>
+                  <c:v>-36.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-11</c:v>
+                  <c:v>-33.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.5</c:v>
+                  <c:v>-29.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>-24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-17.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-14.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-5.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>19.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>FlxTest10mm_2!$C$15:$AI$15</c:f>
+              <c:f>FlxTest10mm_1!$C$15:$AI$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>-12.024486481310953</c:v>
+                  <c:v>-13.550199438030189</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12.010720430450908</c:v>
+                  <c:v>-12.715746326203965</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-12.467074331666348</c:v>
+                  <c:v>-12.227450296743585</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-11.429265093789359</c:v>
+                  <c:v>-13.574295183417183</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-9.361208446969103</c:v>
+                  <c:v>-12.617833179689791</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-7.6761795853386783</c:v>
+                  <c:v>-11.427173303326315</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-4.9579976724776733</c:v>
+                  <c:v>-7.8289359826583684</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1.6722536503811283</c:v>
+                  <c:v>-6.4962395866945686</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.80746439223476663</c:v>
+                  <c:v>-4.9404873370427511</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-3.5743411708348779E-3</c:v>
+                  <c:v>-2.8261340010696823</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-2.0198749999999999</c:v>
+                  <c:v>-1.2108000422274927</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-4.1705971185958441</c:v>
+                  <c:v>-0.11021594724709009</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-6.4666790193515293</c:v>
+                  <c:v>-1.5137448723481624</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-8.1665094852463582</c:v>
+                  <c:v>-3.1927408242720881</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-10.603302506170124</c:v>
+                  <c:v>-4.8615958230354943</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-12.640024275140153</c:v>
+                  <c:v>-6.8694525901110115</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-13.930450567806828</c:v>
+                  <c:v>-8.5997889837959107</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-14.689482923460329</c:v>
+                  <c:v>-10.35823139969961</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-14.674822536018389</c:v>
+                  <c:v>-11.863637901467659</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-13.151302910231001</c:v>
+                  <c:v>-13.477555041999489</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>-13.77813076308844</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>-14.884597105183458</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>-14.534539473342328</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>-14.338144060893327</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>-14.021223986689929</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>-12.539046654783448</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>-11.167854768300959</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0</c:v>
+                  <c:v>-8.2836070695559112</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0</c:v>
@@ -5721,7 +6191,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-9D05-4463-B8B4-EFE1AE46B75E}"/>
+              <c16:uniqueId val="{00000004-B771-4C56-A69D-B7F3E808952B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5953,6 +6423,46 @@
 </file>
 
 <file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -7344,6 +7854,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -11516,6 +12542,49 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>74612</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>331258</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07BDA400-5F04-4953-A0E6-367FC264DFC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -11814,23 +12883,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>740833</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>7937</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>338137</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>131233</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>36512</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>80962</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{739FA640-F8ED-4CD7-A88D-06604D5CF975}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7DDFDBC-593A-4960-B506-B57F628B62F5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11857,23 +12926,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>74612</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>740833</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>7937</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>331258</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>131233</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>36512</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07BDA400-5F04-4953-A0E6-367FC264DFC8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{739FA640-F8ED-4CD7-A88D-06604D5CF975}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12367,7 +13436,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>17.55</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>17.081</v>
@@ -12825,7 +13894,7 @@
       </c>
       <c r="C15">
         <f>C6*SIN(RADIANS(C8))*C12/1000</f>
-        <v>4.6268503604248918</v>
+        <v>0.26363819717520748</v>
       </c>
       <c r="D15">
         <f t="shared" ref="D15:K15" si="1">D6*SIN(RADIANS(D8))*D12/1000</f>
@@ -12964,7 +14033,7 @@
     <row r="18" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C18">
         <f>C6+4.6262</f>
-        <v>22.176200000000001</v>
+        <v>5.6261999999999999</v>
       </c>
       <c r="D18">
         <f t="shared" ref="D18:K18" si="4">D6+4.6262</f>
@@ -13146,6 +14215,825 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245A1644-2BFB-4EA7-BEAA-4598893697AD}">
+  <dimension ref="A1:AJ29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.08984375" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>485</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <f>C2-C2*0.17</f>
+        <v>402.55</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>398</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <f>P5+1</f>
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <f>Q5+1</f>
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <f t="shared" ref="S5:AI5" si="0">R5+1</f>
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="AF5" s="10">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="AG5" s="10">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="AH5" s="10">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="AI5" s="10">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>43.774000000000001</v>
+      </c>
+      <c r="D6">
+        <v>43.682000000000002</v>
+      </c>
+      <c r="E6">
+        <v>45.475000000000001</v>
+      </c>
+      <c r="F6">
+        <v>41.618000000000002</v>
+      </c>
+      <c r="G6">
+        <v>34.204000000000001</v>
+      </c>
+      <c r="H6">
+        <v>27.984999999999999</v>
+      </c>
+      <c r="I6">
+        <v>18.039000000000001</v>
+      </c>
+      <c r="J6">
+        <v>6.0835999999999997</v>
+      </c>
+      <c r="K6">
+        <v>2.9384000000000001</v>
+      </c>
+      <c r="L6">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="M6">
+        <v>7.3449999999999998</v>
+      </c>
+      <c r="N6">
+        <v>15.176</v>
+      </c>
+      <c r="O6">
+        <v>23.530999999999999</v>
+      </c>
+      <c r="P6">
+        <v>29.727</v>
+      </c>
+      <c r="Q6">
+        <v>38.637999999999998</v>
+      </c>
+      <c r="R6">
+        <v>46.064999999999998</v>
+      </c>
+      <c r="S6">
+        <v>50.881999999999998</v>
+      </c>
+      <c r="T6">
+        <v>53.805999999999997</v>
+      </c>
+      <c r="U6">
+        <v>53.527999999999999</v>
+      </c>
+      <c r="V6">
+        <v>48.012999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>5.5</v>
+      </c>
+      <c r="E7">
+        <v>-1</v>
+      </c>
+      <c r="F7">
+        <v>-15</v>
+      </c>
+      <c r="G7">
+        <v>-26.6</v>
+      </c>
+      <c r="H7">
+        <v>-35</v>
+      </c>
+      <c r="I7">
+        <v>-42.5</v>
+      </c>
+      <c r="J7">
+        <v>-56</v>
+      </c>
+      <c r="K7">
+        <v>-56</v>
+      </c>
+      <c r="L7">
+        <v>-63</v>
+      </c>
+      <c r="M7">
+        <v>-64</v>
+      </c>
+      <c r="N7">
+        <v>-55</v>
+      </c>
+      <c r="O7">
+        <v>-48</v>
+      </c>
+      <c r="P7">
+        <v>-42</v>
+      </c>
+      <c r="Q7">
+        <v>-35</v>
+      </c>
+      <c r="R7">
+        <v>-26</v>
+      </c>
+      <c r="S7">
+        <v>-19</v>
+      </c>
+      <c r="T7">
+        <v>-11</v>
+      </c>
+      <c r="U7">
+        <v>0.5</v>
+      </c>
+      <c r="V7">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
+        <v>92.7</v>
+      </c>
+      <c r="D8" s="1">
+        <v>91</v>
+      </c>
+      <c r="E8" s="1">
+        <v>94.5</v>
+      </c>
+      <c r="F8" s="1">
+        <v>93</v>
+      </c>
+      <c r="G8" s="1">
+        <v>95.6</v>
+      </c>
+      <c r="H8" s="1">
+        <v>94.1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>91.9</v>
+      </c>
+      <c r="J8" s="1">
+        <v>91.7</v>
+      </c>
+      <c r="K8" s="1">
+        <v>92.2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>91.1</v>
+      </c>
+      <c r="M8" s="1">
+        <v>90</v>
+      </c>
+      <c r="N8" s="1">
+        <v>92.1</v>
+      </c>
+      <c r="O8" s="1">
+        <v>92.1</v>
+      </c>
+      <c r="P8" s="1">
+        <v>92.6</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>93.7</v>
+      </c>
+      <c r="R8" s="1">
+        <v>93.8</v>
+      </c>
+      <c r="S8" s="1">
+        <v>95.4</v>
+      </c>
+      <c r="T8" s="1">
+        <v>96.9</v>
+      </c>
+      <c r="U8" s="1">
+        <v>94.5</v>
+      </c>
+      <c r="V8" s="1">
+        <v>95.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A9" s="12"/>
+      <c r="B9" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>467</v>
+      </c>
+      <c r="D10">
+        <v>466</v>
+      </c>
+      <c r="E10">
+        <v>463</v>
+      </c>
+      <c r="F10">
+        <v>450</v>
+      </c>
+      <c r="G10">
+        <v>443</v>
+      </c>
+      <c r="H10">
+        <v>431</v>
+      </c>
+      <c r="I10">
+        <v>423</v>
+      </c>
+      <c r="J10">
+        <v>411</v>
+      </c>
+      <c r="K10">
+        <v>408</v>
+      </c>
+      <c r="L10">
+        <v>404</v>
+      </c>
+      <c r="M10">
+        <v>407</v>
+      </c>
+      <c r="N10">
+        <v>413</v>
+      </c>
+      <c r="O10">
+        <v>420</v>
+      </c>
+      <c r="P10">
+        <v>422</v>
+      </c>
+      <c r="Q10">
+        <v>433</v>
+      </c>
+      <c r="R10">
+        <v>442</v>
+      </c>
+      <c r="S10">
+        <v>448</v>
+      </c>
+      <c r="T10">
+        <v>455</v>
+      </c>
+      <c r="U10" s="2">
+        <v>460</v>
+      </c>
+      <c r="V10" s="2">
+        <v>466</v>
+      </c>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="2"/>
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="2"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="2"/>
+      <c r="AI10" s="2"/>
+      <c r="AJ10" s="2"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>275</v>
+      </c>
+      <c r="D12">
+        <v>275</v>
+      </c>
+      <c r="E12">
+        <v>275</v>
+      </c>
+      <c r="F12">
+        <v>275</v>
+      </c>
+      <c r="G12">
+        <v>275</v>
+      </c>
+      <c r="H12">
+        <v>275</v>
+      </c>
+      <c r="I12">
+        <v>275</v>
+      </c>
+      <c r="J12">
+        <v>275</v>
+      </c>
+      <c r="K12">
+        <v>275</v>
+      </c>
+      <c r="L12">
+        <v>275</v>
+      </c>
+      <c r="M12">
+        <v>275</v>
+      </c>
+      <c r="N12">
+        <v>275</v>
+      </c>
+      <c r="O12">
+        <v>275</v>
+      </c>
+      <c r="P12">
+        <v>275</v>
+      </c>
+      <c r="Q12">
+        <v>275</v>
+      </c>
+      <c r="R12">
+        <v>275</v>
+      </c>
+      <c r="S12">
+        <v>275</v>
+      </c>
+      <c r="T12">
+        <v>275</v>
+      </c>
+      <c r="U12">
+        <v>275</v>
+      </c>
+      <c r="V12">
+        <v>275</v>
+      </c>
+      <c r="W12">
+        <v>275</v>
+      </c>
+      <c r="X12">
+        <v>275</v>
+      </c>
+      <c r="Y12">
+        <v>275</v>
+      </c>
+      <c r="Z12">
+        <v>275</v>
+      </c>
+      <c r="AA12">
+        <v>275</v>
+      </c>
+      <c r="AB12">
+        <v>275</v>
+      </c>
+      <c r="AC12">
+        <v>275</v>
+      </c>
+      <c r="AD12">
+        <v>275</v>
+      </c>
+      <c r="AE12">
+        <v>275</v>
+      </c>
+      <c r="AF12">
+        <v>275</v>
+      </c>
+      <c r="AG12">
+        <v>275</v>
+      </c>
+      <c r="AH12">
+        <v>275</v>
+      </c>
+      <c r="AI12">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>45</v>
+      </c>
+      <c r="D13">
+        <v>50</v>
+      </c>
+      <c r="E13">
+        <v>55</v>
+      </c>
+      <c r="F13">
+        <v>65</v>
+      </c>
+      <c r="G13">
+        <v>70</v>
+      </c>
+      <c r="H13">
+        <v>74</v>
+      </c>
+      <c r="I13">
+        <v>73</v>
+      </c>
+      <c r="J13">
+        <v>72</v>
+      </c>
+      <c r="K13">
+        <v>65</v>
+      </c>
+      <c r="L13">
+        <v>63</v>
+      </c>
+      <c r="M13">
+        <v>66</v>
+      </c>
+      <c r="N13">
+        <v>71</v>
+      </c>
+      <c r="O13">
+        <v>75</v>
+      </c>
+      <c r="P13">
+        <v>75</v>
+      </c>
+      <c r="Q13">
+        <v>76</v>
+      </c>
+      <c r="R13">
+        <v>75</v>
+      </c>
+      <c r="S13">
+        <v>69</v>
+      </c>
+      <c r="T13">
+        <v>65</v>
+      </c>
+      <c r="U13">
+        <v>56</v>
+      </c>
+      <c r="V13">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="13"/>
+      <c r="B14" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="B15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <f>C6*-SIN(RADIANS(C8))*C12/1000</f>
+        <v>-12.024486481310953</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ref="D15:AI15" si="1">D6*-SIN(RADIANS(D8))*D12/1000</f>
+        <v>-12.010720430450908</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>-12.467074331666348</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>-11.429265093789359</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>-9.361208446969103</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>-7.6761795853386783</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="1"/>
+        <v>-4.9579976724776733</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>-1.6722536503811283</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>-0.80746439223476663</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>-3.5743411708348779E-3</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="1"/>
+        <v>-2.0198749999999999</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="1"/>
+        <v>-4.1705971185958441</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="1"/>
+        <v>-6.4666790193515293</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="1"/>
+        <v>-8.1665094852463582</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="1"/>
+        <v>-10.603302506170124</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>-12.640024275140153</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="1"/>
+        <v>-13.930450567806828</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="1"/>
+        <v>-14.689482923460329</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="1"/>
+        <v>-14.674822536018389</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="1"/>
+        <v>-13.151302910231001</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="L16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="18:18" x14ac:dyDescent="0.35">
+      <c r="R29">
+        <f>485*1.03</f>
+        <v>499.55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB28D160-17A5-469E-8CF6-067E3CB95279}">
   <dimension ref="A1:AJ29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -17092,7 +18980,7 @@
         <v>3</v>
       </c>
       <c r="C9">
-        <v>340</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>340</v>
@@ -17907,6 +19795,628 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC7A6C4B-FDDD-4D0B-90C8-5B01A1705645}">
+  <dimension ref="A1:AE17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="3"/>
+    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="8" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="14" max="14" width="14.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>408</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="25">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>6</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>8</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9</v>
+      </c>
+      <c r="L5" s="10">
+        <v>10</v>
+      </c>
+      <c r="M5" s="10">
+        <v>11</v>
+      </c>
+      <c r="N5" s="10">
+        <v>12</v>
+      </c>
+      <c r="O5" s="10">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>15</v>
+      </c>
+      <c r="R5" s="10">
+        <v>16</v>
+      </c>
+      <c r="S5" s="10">
+        <v>17</v>
+      </c>
+      <c r="T5" s="10">
+        <v>18</v>
+      </c>
+      <c r="U5" s="10">
+        <v>19</v>
+      </c>
+      <c r="V5" s="10">
+        <v>20</v>
+      </c>
+      <c r="W5" s="10">
+        <v>21</v>
+      </c>
+      <c r="X5" s="10">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="21">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>6.08</v>
+      </c>
+      <c r="E6">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="F6">
+        <v>23.21</v>
+      </c>
+      <c r="G6">
+        <v>30.212</v>
+      </c>
+      <c r="H6">
+        <v>34.454999999999998</v>
+      </c>
+      <c r="I6">
+        <v>35.81</v>
+      </c>
+      <c r="J6">
+        <v>35.049999999999997</v>
+      </c>
+      <c r="K6">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="L6">
+        <v>31</v>
+      </c>
+      <c r="M6">
+        <v>32</v>
+      </c>
+      <c r="N6">
+        <v>39.243000000000002</v>
+      </c>
+      <c r="O6">
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="21">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>38</v>
+      </c>
+      <c r="E7">
+        <v>28</v>
+      </c>
+      <c r="F7">
+        <v>25</v>
+      </c>
+      <c r="G7">
+        <v>15</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>-9</v>
+      </c>
+      <c r="J7">
+        <v>-25</v>
+      </c>
+      <c r="K7">
+        <v>-29</v>
+      </c>
+      <c r="L7">
+        <v>-30</v>
+      </c>
+      <c r="M7">
+        <v>-40</v>
+      </c>
+      <c r="N7">
+        <v>-69</v>
+      </c>
+      <c r="O7">
+        <v>-73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="B8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="21">
+        <v>622.08600000000001</v>
+      </c>
+      <c r="D8">
+        <v>627.41999999999996</v>
+      </c>
+      <c r="E8">
+        <v>628.19100000000003</v>
+      </c>
+      <c r="F8">
+        <v>627.428</v>
+      </c>
+      <c r="G8">
+        <v>626.65499999999997</v>
+      </c>
+      <c r="H8">
+        <v>628.71500000000003</v>
+      </c>
+      <c r="I8">
+        <v>628.19100000000003</v>
+      </c>
+      <c r="J8">
+        <v>627.42600000000004</v>
+      </c>
+      <c r="K8">
+        <v>629.71799999999996</v>
+      </c>
+      <c r="L8">
+        <v>628.95500000000004</v>
+      </c>
+      <c r="M8">
+        <v>627.48</v>
+      </c>
+      <c r="N8">
+        <v>627.48</v>
+      </c>
+      <c r="O8">
+        <v>629.71799999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="20">
+        <v>87</v>
+      </c>
+      <c r="D9" s="1">
+        <v>89</v>
+      </c>
+      <c r="E9" s="1">
+        <v>85</v>
+      </c>
+      <c r="F9" s="1">
+        <v>88</v>
+      </c>
+      <c r="G9" s="1">
+        <v>83</v>
+      </c>
+      <c r="H9" s="1">
+        <v>80</v>
+      </c>
+      <c r="I9" s="1">
+        <v>78.5</v>
+      </c>
+      <c r="J9" s="1">
+        <v>75.5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>75</v>
+      </c>
+      <c r="L9" s="1">
+        <v>77</v>
+      </c>
+      <c r="M9" s="1">
+        <v>75</v>
+      </c>
+      <c r="N9" s="1">
+        <v>75</v>
+      </c>
+      <c r="O9" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="21">
+        <v>339</v>
+      </c>
+      <c r="D10" s="14">
+        <v>334</v>
+      </c>
+      <c r="E10" s="14">
+        <v>346</v>
+      </c>
+      <c r="F10" s="14">
+        <v>349</v>
+      </c>
+      <c r="G10" s="14">
+        <v>360</v>
+      </c>
+      <c r="H10" s="14">
+        <v>372</v>
+      </c>
+      <c r="I10" s="14">
+        <v>378</v>
+      </c>
+      <c r="J10" s="14">
+        <v>382</v>
+      </c>
+      <c r="K10" s="14">
+        <v>382</v>
+      </c>
+      <c r="L10" s="14">
+        <v>383</v>
+      </c>
+      <c r="M10" s="14">
+        <v>387</v>
+      </c>
+      <c r="N10" s="14">
+        <v>397</v>
+      </c>
+      <c r="O10" s="14">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="20"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="21"/>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="21">
+        <v>249.71</v>
+      </c>
+      <c r="D13">
+        <v>249.71</v>
+      </c>
+      <c r="E13">
+        <v>249.71</v>
+      </c>
+      <c r="F13">
+        <v>249.71</v>
+      </c>
+      <c r="G13">
+        <v>249.71</v>
+      </c>
+      <c r="H13">
+        <v>249.71</v>
+      </c>
+      <c r="I13">
+        <v>249.71</v>
+      </c>
+      <c r="J13">
+        <v>249.71</v>
+      </c>
+      <c r="K13">
+        <v>249.71</v>
+      </c>
+      <c r="L13">
+        <v>249.71</v>
+      </c>
+      <c r="M13">
+        <v>249.71</v>
+      </c>
+      <c r="N13">
+        <v>249.71</v>
+      </c>
+      <c r="O13">
+        <v>249.71</v>
+      </c>
+      <c r="P13">
+        <v>249.71</v>
+      </c>
+      <c r="Q13">
+        <v>249.71</v>
+      </c>
+      <c r="R13">
+        <v>249.71</v>
+      </c>
+      <c r="S13">
+        <v>249.71</v>
+      </c>
+      <c r="AA13">
+        <v>249.71</v>
+      </c>
+      <c r="AB13">
+        <v>249.71</v>
+      </c>
+      <c r="AC13">
+        <v>249.71</v>
+      </c>
+      <c r="AD13">
+        <v>249.71</v>
+      </c>
+      <c r="AE13">
+        <v>249.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A14" s="12"/>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="21">
+        <v>84</v>
+      </c>
+      <c r="D14">
+        <v>75</v>
+      </c>
+      <c r="E14">
+        <v>73</v>
+      </c>
+      <c r="F14">
+        <v>65</v>
+      </c>
+      <c r="G14">
+        <v>60</v>
+      </c>
+      <c r="H14">
+        <v>54</v>
+      </c>
+      <c r="I14">
+        <v>46</v>
+      </c>
+      <c r="J14">
+        <v>41.5</v>
+      </c>
+      <c r="K14">
+        <v>40</v>
+      </c>
+      <c r="L14">
+        <v>35</v>
+      </c>
+      <c r="M14">
+        <v>31</v>
+      </c>
+      <c r="N14">
+        <v>27</v>
+      </c>
+      <c r="O14">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="13"/>
+      <c r="B15" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="19"/>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="B16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="21">
+        <f>C6*SIN(RADIANS(C9))*C13/1000</f>
+        <v>0.24936778112356464</v>
+      </c>
+      <c r="D16">
+        <f t="shared" ref="D16:S16" si="0">D6*SIN(RADIANS(D9))*D13/1000</f>
+        <v>1.5180055651816151</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>4.1916022603192538</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>5.7922384740607207</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>7.4880049100902237</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>8.4730476326811974</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>8.7625994980529605</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>8.4735529621225449</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>8.0320045581520194</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="0"/>
+        <v>7.5426084152031541</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="0"/>
+        <v>7.7184428186445837</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="0"/>
+        <v>9.4654641103771695</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="0"/>
+        <v>8.9788371589935139</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <f t="shared" ref="AA16:AE16" si="1">AA6*SIN(RADIANS(AA9))*AA13/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="14:15" x14ac:dyDescent="0.35">
+      <c r="N17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E5B9E9-F1B4-4DAB-B7CA-9BCB2303132C}">
   <dimension ref="A1:AJ15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -18803,823 +21313,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245A1644-2BFB-4EA7-BEAA-4598893697AD}">
-  <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.08984375" style="3"/>
-    <col min="2" max="2" width="19.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
-    <col min="8" max="9" width="13.453125" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>485</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3">
-        <f>C2-C2*0.17</f>
-        <v>402.55</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4">
-        <v>398</v>
-      </c>
-      <c r="L4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1</v>
-      </c>
-      <c r="D5" s="10">
-        <v>2</v>
-      </c>
-      <c r="E5" s="10">
-        <v>3</v>
-      </c>
-      <c r="F5" s="10">
-        <v>4</v>
-      </c>
-      <c r="G5" s="10">
-        <v>5</v>
-      </c>
-      <c r="H5" s="10">
-        <v>6</v>
-      </c>
-      <c r="I5" s="10">
-        <v>7</v>
-      </c>
-      <c r="J5" s="10">
-        <v>8</v>
-      </c>
-      <c r="K5" s="10">
-        <v>9</v>
-      </c>
-      <c r="L5" s="10">
-        <v>10</v>
-      </c>
-      <c r="M5" s="10">
-        <v>11</v>
-      </c>
-      <c r="N5" s="10">
-        <v>12</v>
-      </c>
-      <c r="O5" s="10">
-        <v>13</v>
-      </c>
-      <c r="P5" s="10">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="10">
-        <f>P5+1</f>
-        <v>15</v>
-      </c>
-      <c r="R5" s="10">
-        <f>Q5+1</f>
-        <v>16</v>
-      </c>
-      <c r="S5" s="10">
-        <f t="shared" ref="S5:AI5" si="0">R5+1</f>
-        <v>17</v>
-      </c>
-      <c r="T5" s="10">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="U5" s="10">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="V5" s="10">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="W5" s="10">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="X5" s="10">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="Y5" s="10">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="Z5" s="10">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AA5" s="10">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="AB5" s="10">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="AC5" s="10">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="AD5" s="10">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="AE5" s="10">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="AF5" s="10">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="AG5" s="10">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="AH5" s="10">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="AI5" s="10">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>43.774000000000001</v>
-      </c>
-      <c r="D6">
-        <v>43.682000000000002</v>
-      </c>
-      <c r="E6">
-        <v>45.475000000000001</v>
-      </c>
-      <c r="F6">
-        <v>41.618000000000002</v>
-      </c>
-      <c r="G6">
-        <v>34.204000000000001</v>
-      </c>
-      <c r="H6">
-        <v>27.984999999999999</v>
-      </c>
-      <c r="I6">
-        <v>18.039000000000001</v>
-      </c>
-      <c r="J6">
-        <v>6.0835999999999997</v>
-      </c>
-      <c r="K6">
-        <v>2.9384000000000001</v>
-      </c>
-      <c r="L6">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="M6">
-        <v>7.3449999999999998</v>
-      </c>
-      <c r="N6">
-        <v>15.176</v>
-      </c>
-      <c r="O6">
-        <v>23.530999999999999</v>
-      </c>
-      <c r="P6">
-        <v>29.727</v>
-      </c>
-      <c r="Q6">
-        <v>38.637999999999998</v>
-      </c>
-      <c r="R6">
-        <v>46.064999999999998</v>
-      </c>
-      <c r="S6">
-        <v>50.881999999999998</v>
-      </c>
-      <c r="T6">
-        <v>53.805999999999997</v>
-      </c>
-      <c r="U6">
-        <v>53.527999999999999</v>
-      </c>
-      <c r="V6">
-        <v>48.012999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>5.5</v>
-      </c>
-      <c r="E7">
-        <v>-1</v>
-      </c>
-      <c r="F7">
-        <v>-15</v>
-      </c>
-      <c r="G7">
-        <v>-26.6</v>
-      </c>
-      <c r="H7">
-        <v>-35</v>
-      </c>
-      <c r="I7">
-        <v>-42.5</v>
-      </c>
-      <c r="J7">
-        <v>-56</v>
-      </c>
-      <c r="K7">
-        <v>-56</v>
-      </c>
-      <c r="L7">
-        <v>-63</v>
-      </c>
-      <c r="M7">
-        <v>-64</v>
-      </c>
-      <c r="N7">
-        <v>-55</v>
-      </c>
-      <c r="O7">
-        <v>-48</v>
-      </c>
-      <c r="P7">
-        <v>-42</v>
-      </c>
-      <c r="Q7">
-        <v>-35</v>
-      </c>
-      <c r="R7">
-        <v>-26</v>
-      </c>
-      <c r="S7">
-        <v>-19</v>
-      </c>
-      <c r="T7">
-        <v>-11</v>
-      </c>
-      <c r="U7">
-        <v>0.5</v>
-      </c>
-      <c r="V7">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1">
-        <v>92.7</v>
-      </c>
-      <c r="D8" s="1">
-        <v>91</v>
-      </c>
-      <c r="E8" s="1">
-        <v>94.5</v>
-      </c>
-      <c r="F8" s="1">
-        <v>93</v>
-      </c>
-      <c r="G8" s="1">
-        <v>95.6</v>
-      </c>
-      <c r="H8" s="1">
-        <v>94.1</v>
-      </c>
-      <c r="I8" s="1">
-        <v>91.9</v>
-      </c>
-      <c r="J8" s="1">
-        <v>91.7</v>
-      </c>
-      <c r="K8" s="1">
-        <v>92.2</v>
-      </c>
-      <c r="L8" s="1">
-        <v>91.1</v>
-      </c>
-      <c r="M8" s="1">
-        <v>90</v>
-      </c>
-      <c r="N8" s="1">
-        <v>92.1</v>
-      </c>
-      <c r="O8" s="1">
-        <v>92.1</v>
-      </c>
-      <c r="P8" s="1">
-        <v>92.6</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>93.7</v>
-      </c>
-      <c r="R8" s="1">
-        <v>93.8</v>
-      </c>
-      <c r="S8" s="1">
-        <v>95.4</v>
-      </c>
-      <c r="T8" s="1">
-        <v>96.9</v>
-      </c>
-      <c r="U8" s="1">
-        <v>94.5</v>
-      </c>
-      <c r="V8" s="1">
-        <v>95.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A9" s="12"/>
-      <c r="B9" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
-      <c r="B10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>467</v>
-      </c>
-      <c r="D10">
-        <v>466</v>
-      </c>
-      <c r="E10">
-        <v>463</v>
-      </c>
-      <c r="F10">
-        <v>450</v>
-      </c>
-      <c r="G10">
-        <v>443</v>
-      </c>
-      <c r="H10">
-        <v>431</v>
-      </c>
-      <c r="I10">
-        <v>423</v>
-      </c>
-      <c r="J10">
-        <v>411</v>
-      </c>
-      <c r="K10">
-        <v>408</v>
-      </c>
-      <c r="L10">
-        <v>404</v>
-      </c>
-      <c r="M10">
-        <v>407</v>
-      </c>
-      <c r="N10">
-        <v>413</v>
-      </c>
-      <c r="O10">
-        <v>420</v>
-      </c>
-      <c r="P10">
-        <v>422</v>
-      </c>
-      <c r="Q10">
-        <v>433</v>
-      </c>
-      <c r="R10">
-        <v>442</v>
-      </c>
-      <c r="S10">
-        <v>448</v>
-      </c>
-      <c r="T10">
-        <v>455</v>
-      </c>
-      <c r="U10" s="2">
-        <v>460</v>
-      </c>
-      <c r="V10" s="2">
-        <v>466</v>
-      </c>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
-      <c r="AB10" s="2"/>
-      <c r="AC10" s="2"/>
-      <c r="AD10" s="2"/>
-      <c r="AE10" s="2"/>
-      <c r="AF10" s="2"/>
-      <c r="AG10" s="2"/>
-      <c r="AH10" s="2"/>
-      <c r="AI10" s="2"/>
-      <c r="AJ10" s="2"/>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A12" s="12"/>
-      <c r="B12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>275</v>
-      </c>
-      <c r="D12">
-        <v>275</v>
-      </c>
-      <c r="E12">
-        <v>275</v>
-      </c>
-      <c r="F12">
-        <v>275</v>
-      </c>
-      <c r="G12">
-        <v>275</v>
-      </c>
-      <c r="H12">
-        <v>275</v>
-      </c>
-      <c r="I12">
-        <v>275</v>
-      </c>
-      <c r="J12">
-        <v>275</v>
-      </c>
-      <c r="K12">
-        <v>275</v>
-      </c>
-      <c r="L12">
-        <v>275</v>
-      </c>
-      <c r="M12">
-        <v>275</v>
-      </c>
-      <c r="N12">
-        <v>275</v>
-      </c>
-      <c r="O12">
-        <v>275</v>
-      </c>
-      <c r="P12">
-        <v>275</v>
-      </c>
-      <c r="Q12">
-        <v>275</v>
-      </c>
-      <c r="R12">
-        <v>275</v>
-      </c>
-      <c r="S12">
-        <v>275</v>
-      </c>
-      <c r="T12">
-        <v>275</v>
-      </c>
-      <c r="U12">
-        <v>275</v>
-      </c>
-      <c r="V12">
-        <v>275</v>
-      </c>
-      <c r="W12">
-        <v>275</v>
-      </c>
-      <c r="X12">
-        <v>275</v>
-      </c>
-      <c r="Y12">
-        <v>275</v>
-      </c>
-      <c r="Z12">
-        <v>275</v>
-      </c>
-      <c r="AA12">
-        <v>275</v>
-      </c>
-      <c r="AB12">
-        <v>275</v>
-      </c>
-      <c r="AC12">
-        <v>275</v>
-      </c>
-      <c r="AD12">
-        <v>275</v>
-      </c>
-      <c r="AE12">
-        <v>275</v>
-      </c>
-      <c r="AF12">
-        <v>275</v>
-      </c>
-      <c r="AG12">
-        <v>275</v>
-      </c>
-      <c r="AH12">
-        <v>275</v>
-      </c>
-      <c r="AI12">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A13" s="12"/>
-      <c r="B13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13">
-        <v>45</v>
-      </c>
-      <c r="D13">
-        <v>50</v>
-      </c>
-      <c r="E13">
-        <v>55</v>
-      </c>
-      <c r="F13">
-        <v>65</v>
-      </c>
-      <c r="G13">
-        <v>70</v>
-      </c>
-      <c r="H13">
-        <v>74</v>
-      </c>
-      <c r="I13">
-        <v>73</v>
-      </c>
-      <c r="J13">
-        <v>72</v>
-      </c>
-      <c r="K13">
-        <v>65</v>
-      </c>
-      <c r="L13">
-        <v>63</v>
-      </c>
-      <c r="M13">
-        <v>66</v>
-      </c>
-      <c r="N13">
-        <v>71</v>
-      </c>
-      <c r="O13">
-        <v>75</v>
-      </c>
-      <c r="P13">
-        <v>75</v>
-      </c>
-      <c r="Q13">
-        <v>76</v>
-      </c>
-      <c r="R13">
-        <v>75</v>
-      </c>
-      <c r="S13">
-        <v>69</v>
-      </c>
-      <c r="T13">
-        <v>65</v>
-      </c>
-      <c r="U13">
-        <v>56</v>
-      </c>
-      <c r="V13">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="B15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <f>C6*-SIN(RADIANS(C8))*C12/1000</f>
-        <v>-12.024486481310953</v>
-      </c>
-      <c r="D15">
-        <f t="shared" ref="D15:AI15" si="1">D6*-SIN(RADIANS(D8))*D12/1000</f>
-        <v>-12.010720430450908</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="1"/>
-        <v>-12.467074331666348</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>-11.429265093789359</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>-9.361208446969103</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>-7.6761795853386783</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>-4.9579976724776733</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>-1.6722536503811283</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>-0.80746439223476663</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="1"/>
-        <v>-3.5743411708348779E-3</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="1"/>
-        <v>-2.0198749999999999</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="1"/>
-        <v>-4.1705971185958441</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="1"/>
-        <v>-6.4666790193515293</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="1"/>
-        <v>-8.1665094852463582</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="1"/>
-        <v>-10.603302506170124</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="1"/>
-        <v>-12.640024275140153</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="1"/>
-        <v>-13.930450567806828</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="1"/>
-        <v>-14.689482923460329</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="1"/>
-        <v>-14.674822536018389</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="1"/>
-        <v>-13.151302910231001</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="L16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="18:18" x14ac:dyDescent="0.35">
-      <c r="R29">
-        <f>485*1.03</f>
-        <v>499.55</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>